--- a/Database_Lib.xlsx
+++ b/Database_Lib.xlsx
@@ -8,16 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\altium\Altium_Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2EB328-8712-4870-8508-9B57F4496228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A755750-FF16-4A37-8779-0E3068644DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4968" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Resistor" sheetId="1" r:id="rId1"/>
+    <sheet name="Resistor" sheetId="3" r:id="rId1"/>
+    <sheet name="Capacitor" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Resistor!$A$1:$I$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
   <si>
     <t>GOST_VALUE</t>
   </si>
@@ -97,6 +95,42 @@
   </si>
   <si>
     <t>RC0402FR-070RL</t>
+  </si>
+  <si>
+    <t>50В</t>
+  </si>
+  <si>
+    <t>0,1 мкФ</t>
+  </si>
+  <si>
+    <t>С0603</t>
+  </si>
+  <si>
+    <t>0.1uF</t>
+  </si>
+  <si>
+    <t>10%</t>
+  </si>
+  <si>
+    <t>GOST_TKE</t>
+  </si>
+  <si>
+    <t>X7R</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB104</t>
+  </si>
+  <si>
+    <t>Capacitor</t>
+  </si>
+  <si>
+    <t>5.1 кОм</t>
+  </si>
+  <si>
+    <t>5.1k</t>
+  </si>
+  <si>
+    <t>RC0603FR-075K1L</t>
   </si>
 </sst>
 </file>
@@ -429,19 +463,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DB4D5C-124F-40F8-A1BC-9516EF6D22C9}">
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -533,13 +567,128 @@
         <v>Resistor 0603 (1608) 0.1 Вт 0 Ом 1%</v>
       </c>
     </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="str">
+        <f>F4 &amp;" "&amp;B4&amp;" "&amp;C4&amp;" "&amp;D4&amp;" "&amp;E4</f>
+        <v>Resistor 0603 (1608) 0.1 Вт 5.1 кОм 1%</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I3">
-      <sortCondition ref="D1"/>
-    </sortState>
-  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I3">
+    <sortCondition ref="D2:D3"/>
+  </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FED977-E1E5-4AD4-AEED-B08864737075}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="34" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" t="str">
+        <f>G2 &amp;" "&amp;B2&amp;" "&amp;C2&amp;" "&amp;D2&amp;" "&amp;E2</f>
+        <v>Capacitor 0402 (1005) 50В 0,1 мкФ 10%</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Database_Lib.xlsx
+++ b/Database_Lib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\altium\Altium_Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A755750-FF16-4A37-8779-0E3068644DBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF46701B-D242-4139-9EBB-A97EE2CD8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resistor" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
   <si>
     <t>GOST_VALUE</t>
   </si>
@@ -131,6 +131,36 @@
   </si>
   <si>
     <t>RC0603FR-075K1L</t>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB105</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
+  </si>
+  <si>
+    <t>1 мкФ</t>
+  </si>
+  <si>
+    <t>2,2 мкФ</t>
+  </si>
+  <si>
+    <t>CC0603KRX5R8BB225</t>
+  </si>
+  <si>
+    <t>25В</t>
+  </si>
+  <si>
+    <t>X5R</t>
+  </si>
+  <si>
+    <t>22 Ом</t>
+  </si>
+  <si>
+    <t>RC0603FR-0722RL</t>
   </si>
 </sst>
 </file>
@@ -464,7 +494,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DB4D5C-124F-40F8-A1BC-9516EF6D22C9}">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
@@ -597,18 +627,49 @@
         <v>Resistor 0603 (1608) 0.1 Вт 5.1 кОм 1%</v>
       </c>
     </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H5">
+        <v>22</v>
+      </c>
+      <c r="I5" t="str">
+        <f>F5 &amp;" "&amp;B5&amp;" "&amp;C5&amp;" "&amp;D5&amp;" "&amp;E5</f>
+        <v>Resistor 0603 (1608) 0.1 Вт 22 Ом 1%</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I3">
     <sortCondition ref="D2:D3"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FED977-E1E5-4AD4-AEED-B08864737075}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
@@ -688,7 +749,74 @@
         <v>Capacitor 0402 (1005) 50В 0,1 мкФ 10%</v>
       </c>
     </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J4" si="0">G3 &amp;" "&amp;B3&amp;" "&amp;C3&amp;" "&amp;D3&amp;" "&amp;E3</f>
+        <v>Capacitor 0603 (1608) 50В 1 мкФ 10%</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>Capacitor 0603 (1608) 25В 2,2 мкФ 10%</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/Database_Lib.xlsx
+++ b/Database_Lib.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\altium\Altium_Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF46701B-D242-4139-9EBB-A97EE2CD8E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32715D3A-6343-4C89-9211-FBE8AC80EEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2124" yWindow="2124" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resistor" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="43">
   <si>
     <t>GOST_VALUE</t>
   </si>
@@ -103,9 +103,6 @@
     <t>0,1 мкФ</t>
   </si>
   <si>
-    <t>С0603</t>
-  </si>
-  <si>
     <t>0.1uF</t>
   </si>
   <si>
@@ -161,6 +158,15 @@
   </si>
   <si>
     <t>RC0603FR-0722RL</t>
+  </si>
+  <si>
+    <t>GOST_MANUFACTURER</t>
+  </si>
+  <si>
+    <t>Yageo</t>
+  </si>
+  <si>
+    <t>C0603</t>
   </si>
 </sst>
 </file>
@@ -494,172 +500,188 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06DB4D5C-124F-40F8-A1BC-9516EF6D22C9}">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="33.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="I2" t="str">
-        <f>F2 &amp;" "&amp;B2&amp;" "&amp;C2&amp;" "&amp;D2&amp;" "&amp;E2</f>
+      <c r="J2" t="str">
+        <f>G2 &amp;" "&amp;C2&amp;" "&amp;D2&amp;" "&amp;E2&amp;" "&amp;F2</f>
         <v>Resistor 0402 (1005) 0.1 Вт 0 Ом 1%</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="I3" t="str">
-        <f>F3 &amp;" "&amp;B3&amp;" "&amp;C3&amp;" "&amp;D3&amp;" "&amp;E3</f>
+      <c r="J3" t="str">
+        <f>G3 &amp;" "&amp;C3&amp;" "&amp;D3&amp;" "&amp;E3&amp;" "&amp;F3</f>
         <v>Resistor 0603 (1608) 0.1 Вт 0 Ом 1%</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="J4" t="str">
+        <f>G4 &amp;" "&amp;C4&amp;" "&amp;D4&amp;" "&amp;E4&amp;" "&amp;F4</f>
+        <v>Resistor 0603 (1608) 0.1 Вт 5.1 кОм 1%</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" t="str">
-        <f>F4 &amp;" "&amp;B4&amp;" "&amp;C4&amp;" "&amp;D4&amp;" "&amp;E4</f>
-        <v>Resistor 0603 (1608) 0.1 Вт 5.1 кОм 1%</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>22</v>
       </c>
-      <c r="I5" t="str">
-        <f>F5 &amp;" "&amp;B5&amp;" "&amp;C5&amp;" "&amp;D5&amp;" "&amp;E5</f>
+      <c r="J5" t="str">
+        <f>G5 &amp;" "&amp;C5&amp;" "&amp;D5&amp;" "&amp;E5&amp;" "&amp;F5</f>
         <v>Resistor 0603 (1608) 0.1 Вт 22 Ом 1%</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I3">
-    <sortCondition ref="D2:D3"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J3">
+    <sortCondition ref="E2:E3"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -669,148 +691,161 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62FED977-E1E5-4AD4-AEED-B08864737075}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="34" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
       <c r="B1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>12</v>
+      <c r="H2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" t="str">
+        <f>H2 &amp;" "&amp;C2&amp;" "&amp;D2&amp;" "&amp;E2&amp;" "&amp;F2</f>
+        <v>Capacitor 0402 (1005) 50В 0,1 мкФ 10%</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="I3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" t="str">
+        <f t="shared" ref="K3:K4" si="0">H3 &amp;" "&amp;C3&amp;" "&amp;D3&amp;" "&amp;E3&amp;" "&amp;F3</f>
+        <v>Capacitor 0603 (1608) 50В 1 мкФ 10%</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="str">
-        <f>G2 &amp;" "&amp;B2&amp;" "&amp;C2&amp;" "&amp;D2&amp;" "&amp;E2</f>
-        <v>Capacitor 0402 (1005) 50В 0,1 мкФ 10%</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="G4" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4" t="s">
         <v>32</v>
       </c>
-      <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="0">G3 &amp;" "&amp;B3&amp;" "&amp;C3&amp;" "&amp;D3&amp;" "&amp;E3</f>
-        <v>Capacitor 0603 (1608) 50В 1 мкФ 10%</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <f t="shared" si="0"/>
         <v>Capacitor 0603 (1608) 25В 2,2 мкФ 10%</v>
       </c>
